--- a/healthcare_forms/003_patient_information--healthcare_forms.xlsx
+++ b/healthcare_forms/003_patient_information--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>general_surgery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>General Surgery</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>general_surgery</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pulmonology</t>
+          <t>neurosurgery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Neurosurgery</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>emergency_services_choices</t>
+          <t>medical_specialties_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neurosurgery</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Neurosurgery</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>general_medicine</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dermatology</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>urology</t>
+          <t>ophthalmology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Urology</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ophthalmology</t>
+          <t>general_surgery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>General Surgery</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>general_surgery</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pulmonology</t>
+          <t>neurosurgery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Neurosurgery</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_providers_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>neurosurgery</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Neurosurgery</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>general_medicine</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dermatology</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Neurology</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>urology</t>
+          <t>ophthalmology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Urology</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ophthalmology</t>
+          <t>general_surgery</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>General Surgery</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>medical_providers_choices</t>
+          <t>patient_caregivers_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>general_surgery</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>neighbor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Neighbor</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>neighbor</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neighbor</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>patient_caregivers_choices</t>
+          <t>patient_caregiver_relationship_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>primary_caregiver</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Primary Caregiver</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>primary_caregiver</t>
+          <t>secondary_caregiver</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Primary Caregiver</t>
+          <t>Secondary Caregiver</t>
         </is>
       </c>
     </row>
@@ -1675,27 +1675,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>secondary_caregiver</t>
+          <t>tertiary_caregiver</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>Secondary Caregiver</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>patient_caregiver_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>tertiary_caregiver</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>Tertiary Caregiver</t>
         </is>
